--- a/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F62EB13-524D-47A4-92AE-100F12411C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C6FCFD9-20B3-4AAD-A3C9-4C3859047332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" xr2:uid="{7F8A0A69-9CEB-4144-BE0A-0EF5A02E354F}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" xr2:uid="{35D4BDCC-F0F6-46AE-8E95-4FDEDB780BC1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A92291A-D775-4772-9492-A44B57D1DAE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AED2AAC-9C9C-4740-B9FE-112C9373799A}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C6FCFD9-20B3-4AAD-A3C9-4C3859047332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB14DC13-5856-43C2-BA21-CFFF46E6BF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" xr2:uid="{35D4BDCC-F0F6-46AE-8E95-4FDEDB780BC1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5ABAD014-AE5C-451F-87F9-77E7F7BEC6DF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AED2AAC-9C9C-4740-B9FE-112C9373799A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9D3BB8-9BD9-4EDE-B42D-D921925DD3D6}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB14DC13-5856-43C2-BA21-CFFF46E6BF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F51A7C27-2DEC-416D-90F9-0BD524BF6605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5ABAD014-AE5C-451F-87F9-77E7F7BEC6DF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A5E308B7-4ED0-4F4F-B9A3-4B72F52470BD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9D3BB8-9BD9-4EDE-B42D-D921925DD3D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569DE9DE-DBC5-45DD-A744-58AB67EECB15}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F51A7C27-2DEC-416D-90F9-0BD524BF6605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A7C0A50-E343-4833-9FA3-66286F978F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A5E308B7-4ED0-4F4F-B9A3-4B72F52470BD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{808B6386-9F42-4AA6-A8B4-BAD9FDF7D73C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569DE9DE-DBC5-45DD-A744-58AB67EECB15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF115D5-1319-473B-9ACA-8C4D1247C551}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A7C0A50-E343-4833-9FA3-66286F978F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2034C9B0-ABB9-4A29-84AB-7038A483B043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{808B6386-9F42-4AA6-A8B4-BAD9FDF7D73C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{461E4E2A-2233-4E4D-AA5C-8FBE98A7A2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF115D5-1319-473B-9ACA-8C4D1247C551}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0355EF5-0602-4DE6-A149-CA2054B8880D}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2034C9B0-ABB9-4A29-84AB-7038A483B043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1934DAB4-5FA1-4FD9-A971-064F40805A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{461E4E2A-2233-4E4D-AA5C-8FBE98A7A2BE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{15C33CB9-08B7-4591-9C6E-CB8627515AEF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0355EF5-0602-4DE6-A149-CA2054B8880D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F33A3C5-536F-4605-A34E-B62187CBB7A8}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
